--- a/AAII_Financials/Quarterly/DLTR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DLTR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
   <si>
     <t>DLTR</t>
   </si>
@@ -656,515 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E7" s="2">
         <v>46144</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45962</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45871</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45780</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45689</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45598</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45507</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45416</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45325</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45136</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45045</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44954</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44863</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44772</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44590</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44499</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44317</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44226</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44044</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43953</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43862</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43771</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43680</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43589</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43498</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43407</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43316</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43225</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43134</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43036</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42945</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42854</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42763</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4891200</v>
+      </c>
+      <c r="E8" s="3">
         <v>4975800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5450700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4751000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4570400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4639700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4999800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4341200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4068600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4168900</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O8" s="3">
         <v>7314800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7325300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7323800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7720700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>6939900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6768500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>6902600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7080600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6417700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6343200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6479700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6767900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6177000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6277600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6286800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6315300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5746200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5740600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5808700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6205200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5538800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5525600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5553700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>6360600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>5316600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>5281200</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>5287100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>5635500</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>5001600</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3160900</v>
+      </c>
+      <c r="E9" s="3">
         <v>3141000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3259500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3045800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2996700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2987000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3116900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2803900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2674200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2689100</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O9" s="3">
         <v>5136100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5185400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5089100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5330700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4865100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4640900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4559600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4940300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4651700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4479200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4512700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4615100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4252600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4361400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4491900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4354800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4041700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4092100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4081500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4293100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3866900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3861700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3854100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4259600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>3650600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>3653400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>3660000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>3828200</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>3481100</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1730300</v>
+      </c>
+      <c r="E10" s="3">
         <v>1834800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2191200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1705200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1573700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1652700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1882900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1537300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1394400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1479800</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O10" s="3">
         <v>2178700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2139900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2234700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2390000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2074800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2127600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2343000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2140300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1766000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1864000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1967000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2152800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1924400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1916200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1794900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1960500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1704500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1648500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1727200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1912100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1671900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1663900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1699600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2101000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1666000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>1627800</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1627100</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>1807300</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1520500</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,32 +1467,35 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-400400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-26300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>41900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-23800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-8000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-62000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>22100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1492,12 +1511,12 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>30000</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1507,11 +1526,11 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1519,36 +1538,36 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>8400</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
         <v>330600</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3">
         <v>2727000</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
         <v>0</v>
       </c>
@@ -1556,70 +1575,73 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>-35000</v>
       </c>
-      <c r="AL14" s="3">
-        <v>0</v>
-      </c>
       <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>2600</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>50900</v>
       </c>
-      <c r="AO14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AP14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>179800</v>
+      </c>
+      <c r="E15" s="3">
         <v>177000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>170500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>164500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>162000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>151100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>149800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>135500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>122600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>119000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>226200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>215800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>202600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>196400</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1695,8 +1717,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,252 +1761,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4587500</v>
+      </c>
+      <c r="E17" s="3">
         <v>4523600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4714100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4431500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4347400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4255600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4414100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4010500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3852800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3787000</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="3">
         <v>7013100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7037500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6874100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7102600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6558600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>6263100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>6171100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6501800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6107200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5941000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5959800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6086300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5711500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5902700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5920900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6065900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5387800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5471700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5423200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>8352600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5151000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5143100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5116100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5595000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4891400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>4861700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>4898300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>5049000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>4659200</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>303700</v>
+      </c>
+      <c r="E18" s="3">
         <v>452200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>736600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>319500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>223000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>384100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>585700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>330700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>215800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>381900</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="3">
         <v>301700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>287800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>449700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>618100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>381300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>505400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>731500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>578800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>310500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>402200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>519900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>681600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>465500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>374900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>365900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>249400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>358400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>268900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>385500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-2147400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>387800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>382500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>437600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>765600</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>425200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>419500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>388800</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>586500</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>342400</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,297 +2056,304 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-200</v>
-      </c>
-      <c r="E20" s="3">
-        <v>100</v>
       </c>
       <c r="F20" s="3">
         <v>100</v>
       </c>
       <c r="G20" s="3">
+        <v>100</v>
+      </c>
+      <c r="H20" s="3">
         <v>-400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-28100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-32900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-30700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-34000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-79600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-33600</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-33000</v>
       </c>
       <c r="X20" s="3">
         <v>-33000</v>
       </c>
       <c r="Y20" s="3">
+        <v>-33000</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-34200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-38200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-35000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-40700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-39900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-41500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-40500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-41600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-46700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-47800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-44800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-230200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-74100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-70100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-75900</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-75000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-88800</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-112200</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>483600</v>
+      </c>
+      <c r="E21" s="3">
         <v>629400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>907000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>483900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>385400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>534900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>734800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>466100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>338400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>500800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>226200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>517300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>490500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>646000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>786500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>537400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>668200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>886400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>687900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>455400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>545300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>659600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>830300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>597400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>508000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>490700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>388600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>476900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>383500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>495100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-2027400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>490400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>490200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>358900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>848100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>504500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>494900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>467700</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>653400</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>387800</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E22" s="3">
         <v>16300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>18100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>21900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>22800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>22700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>22600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>28300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>29900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>26700</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="3">
         <v>30400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>24200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>25900</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -2366,14 +2405,14 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-      <c r="AI22" s="3" t="s">
-        <v>8</v>
+      <c r="AI22" s="3">
+        <v>0</v>
       </c>
       <c r="AJ22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK22" s="3">
-        <v>0</v>
+      <c r="AK22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL22" s="3">
         <v>0</v>
@@ -2390,252 +2429,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>686400</v>
+      </c>
+      <c r="E23" s="3">
         <v>462400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>676500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>321300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>208600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>423100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>540300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>302300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>185900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>355100</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="3">
         <v>271100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>263700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>393700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>590000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>348400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>474700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>697500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>499200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>276900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>369200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>486900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>647400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>427300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>339900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>325200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>209500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>316900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>228400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>343900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2194100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>340000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>337700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>207400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>691500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>355100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>343600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>313800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>497700</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>230200</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>171900</v>
+      </c>
+      <c r="E24" s="3">
         <v>115100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>164800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>76700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>53100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>109600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>140100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>70000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>43600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>87400</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="3">
         <v>59100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>63300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>94700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>137800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>81500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>114800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>161100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>45000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>60100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>86800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>112400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>144600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>97300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>78400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>77600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>86500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>61100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>48100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>76000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>112900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>58200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>63800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>46900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>213400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>115200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>109800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>113300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>175900</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>58600</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,252 +2804,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>514500</v>
+      </c>
+      <c r="E26" s="3">
         <v>347300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>511700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>244600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>155500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>313500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>400200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>232300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>142300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>267700</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O26" s="3">
         <v>212000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>200400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>299000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>452200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>266900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>359900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>536400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>454200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>216800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>282400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>374500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>502800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>330000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>261500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>247600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>123000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>255800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>180300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>267900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-2307000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>281800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>273900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>160500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>478100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>239900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>233800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>200500</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>321800</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>171600</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>514500</v>
+      </c>
+      <c r="E27" s="3">
         <v>347300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>506100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>244600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>188400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>343400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3695900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>233300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>132400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>300100</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O27" s="3">
         <v>212000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>200400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>299000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>452200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>266900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>359900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>536400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>454200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>216800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>282400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>374500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>502800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>330000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>261500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>247600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>123000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>255800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>180300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>267900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-2307000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>281800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>273900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>160500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>478100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>239900</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>233800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>200500</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>321800</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>171600</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3131,32 +3191,32 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>-5600</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>32900</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>29900</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-4096100</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>1000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-9900</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>32400</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
@@ -3208,8 +3268,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -3226,12 +3286,12 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>562000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,252 +3554,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
         <v>200</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-100</v>
       </c>
       <c r="F32" s="3">
         <v>-100</v>
       </c>
       <c r="G32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H32" s="3">
         <v>400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>28100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>32900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>30700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>34000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>79600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>33600</v>
-      </c>
-      <c r="W32" s="3">
-        <v>33000</v>
       </c>
       <c r="X32" s="3">
         <v>33000</v>
       </c>
       <c r="Y32" s="3">
+        <v>33000</v>
+      </c>
+      <c r="Z32" s="3">
         <v>34200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>38200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>35000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>40700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>39900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>41500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>40500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>41600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>46700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>47800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>44800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>230200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>74100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>70100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>75900</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>75000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>88800</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>112200</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>514500</v>
+      </c>
+      <c r="E33" s="3">
         <v>347300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>506100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>244600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>188400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>343400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3695900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>233300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>132400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>300100</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O33" s="3">
         <v>212000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>200400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>299000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>452200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>266900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>359900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>536400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>454200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>216800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>282400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>374500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>502800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>330000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>261500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>247600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>123000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>255800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>180300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>267900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-2307000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>281800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>273900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>160500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1040100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>239900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>233800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>200500</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>321800</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>171600</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,257 +3929,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>514500</v>
+      </c>
+      <c r="E35" s="3">
         <v>347300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>506100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>244600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>188400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>343400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3695900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>233300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>132400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>300100</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O35" s="3">
         <v>212000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>200400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>299000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>452200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>266900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>359900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>536400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>454200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>216800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>282400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>374500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>502800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>330000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>261500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>247600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>123000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>255800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>180300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>267900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-2307000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>281800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>273900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>160500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1040100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>239900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>233800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>200500</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>321800</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>171600</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E38" s="2">
         <v>46144</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45962</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45871</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45780</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45689</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45598</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45507</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45416</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45325</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45136</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45045</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44954</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44863</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44772</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44590</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44499</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44317</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44226</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44044</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43953</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43862</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43771</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43680</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43589</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43498</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43407</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43316</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43225</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43134</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43036</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42945</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42854</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42763</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,130 +4276,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1058100</v>
+      </c>
+      <c r="E41" s="3">
         <v>1007300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>717800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>594800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>666300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1007400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1256500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>697600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>570300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>618500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>425200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>444600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>512700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>872800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>642800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>439000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>688900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1218500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>984900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>701400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>720800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1473900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1416700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1118300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1750300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1755100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>539200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>433700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>623400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>725800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>422100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>708300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>647300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>475200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1097800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>400100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>693300</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1154900</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>866400</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>733800</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4424,7 +4513,7 @@
         <v>0</v>
       </c>
       <c r="AM42" s="3">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="AN42" s="3">
         <v>4000</v>
@@ -4435,8 +4524,11 @@
       <c r="AP42" s="3">
         <v>4000</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>4000</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4479,8 +4571,8 @@
       <c r="P43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -4557,374 +4649,386 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2452200</v>
+      </c>
+      <c r="E44" s="3">
         <v>2470800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2495400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2859700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2683400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2704000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2672000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5535100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5101600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5009000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2495800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5515100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5329400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5112000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5449300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5657700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5422200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4801100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4367300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4316000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3667700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3604600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3427000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3792300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3275700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3198500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3522000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3882900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3470900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3325500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3536000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3715600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3288200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>3248200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>3169300</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>3397800</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>2928500</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>2878400</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>2865800</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>3273900</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>234300</v>
+      </c>
+      <c r="E45" s="3">
         <v>220300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>233000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>276000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>250700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4885300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5178700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>398800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>420400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>454700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3211700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>342400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>315300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>282800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>275000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>349900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>266200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>262700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>257000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>357100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>259600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>226400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>207100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>260400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>206500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>211800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>208200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>255700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>246500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>194800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>335200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>325600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>337300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>318600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>309200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>174700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>189400</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>240800</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>201800</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>330700</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3744600</v>
+      </c>
+      <c r="E46" s="3">
         <v>3698400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3446200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3730500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3613900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8596700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9107200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6631500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6092300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6082200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6132700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6302100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6157400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6267600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6367100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6446600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6377300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6282300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5609200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5374500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4648100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5304900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5050800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5171000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5232500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5165400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4269400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4572300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4340800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4246100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4293300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4749500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4272800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4042000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4576300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>3972600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>3815200</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>4278100</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>3938000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>4342400</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4967,8 +5071,8 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -5022,275 +5126,284 @@
         <v>0</v>
       </c>
       <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>334500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>354900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>375300</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>398000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>420400</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>443400</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>468600</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>493800</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9660000</v>
+      </c>
+      <c r="E48" s="3">
         <v>9506300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9394700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9296000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9045600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>8793500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>8645700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13397000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13232700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12771000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>7494800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12482500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12030100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11615200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11430200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11237200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11086500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10878900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10902600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>10801400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>10591400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10538900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>10440400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>10280700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>10236700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>10111800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>10106800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>9675300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>9680500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>9636000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3734000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3720800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3316100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3249700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3200700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3178900</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>3115400</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>3093900</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>3115800</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>3176300</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>422100</v>
+      </c>
+      <c r="E49" s="3">
         <v>423000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>423200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>422200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>422400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>422600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>421200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3062800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3063000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3063300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>423300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5081900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5083300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5082600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5083100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5082400</v>
-      </c>
-      <c r="S49" s="3">
-        <v>5084300</v>
       </c>
       <c r="T49" s="3">
         <v>5084300</v>
       </c>
       <c r="U49" s="3">
+        <v>5084300</v>
+      </c>
+      <c r="V49" s="3">
         <v>5084400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5085300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>5085100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5085600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5084400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5083100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5083000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5081400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5083300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5396500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>5396300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>5395900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5396600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>8128200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>8128600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>8128900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>8130000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>8129200</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>8130100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>8127400</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>8128600</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>8128100</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>201200</v>
+      </c>
+      <c r="E52" s="3">
         <v>194400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>201100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>205600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>217500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>209700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>209300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>236200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>221100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>185000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7963700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>153600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>144100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>129300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>141700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>143300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>128200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>126800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>125600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>128800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>120600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>121300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>120400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>117400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>118800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>113200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>115100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>98000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>76200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>76300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>77300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>50800</v>
-      </c>
-      <c r="AI52" s="3">
-        <v>51600</v>
       </c>
       <c r="AJ52" s="3">
         <v>51600</v>
       </c>
       <c r="AK52" s="3">
+        <v>51600</v>
+      </c>
+      <c r="AL52" s="3">
         <v>50500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>51500</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>51200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>51900</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>50600</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14029600</v>
+      </c>
+      <c r="E54" s="3">
         <v>13823800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13466200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13656300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13384900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>18291200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>18644000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23332800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>22616600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>22110200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>22023500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>24031200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23428000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>23108600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>23022100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>22909500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>22676300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>22372300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>21721800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>21390000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>20445200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>21050700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>20696000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>20652200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>20671000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>20471800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>19574600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>19742100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>19493800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>19354300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>13501200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>16649300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>16103600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>15827100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>16332800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>15730200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>15532300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>15994700</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>15701600</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>16195000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,189 +6116,193 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1626500</v>
+      </c>
+      <c r="E57" s="3">
         <v>1563800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1530700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1676100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1593800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1572000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1705800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2945100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2236100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2266800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1167100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1857000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1776400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1597600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1899800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1864200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2011300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1794100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1884200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1984800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1559600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1520700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1480500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1587200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1481000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1336900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1336500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1473100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1455400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1186500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1416400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1365100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1241700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1181500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1174800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1181300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1196300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1223900</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1119600</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1266400</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1011000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1005200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1000200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1595100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1276200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1971300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1960700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2539500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2786300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1509600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>899800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1723300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1478600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1456900</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R58" s="3">
+      <c r="R58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S58" s="3">
         <v>350000</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -6181,19 +6314,19 @@
         <v>0</v>
       </c>
       <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
         <v>300000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>800000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1050000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>250000</v>
-      </c>
-      <c r="AD58" s="3">
-        <v>750000</v>
       </c>
       <c r="AE58" s="3">
         <v>750000</v>
@@ -6202,7 +6335,7 @@
         <v>750000</v>
       </c>
       <c r="AG58" s="3">
-        <v>0</v>
+        <v>750000</v>
       </c>
       <c r="AH58" s="3">
         <v>0</v>
@@ -6214,10 +6347,10 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="3">
         <v>915900</v>
-      </c>
-      <c r="AL58" s="3">
-        <v>165900</v>
       </c>
       <c r="AM58" s="3">
         <v>165900</v>
@@ -6226,501 +6359,516 @@
         <v>165900</v>
       </c>
       <c r="AO58" s="3">
+        <v>165900</v>
+      </c>
+      <c r="AP58" s="3">
         <v>152100</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>145800</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>665600</v>
+      </c>
+      <c r="E59" s="3">
         <v>615400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>204800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>618600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>616900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4693500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4542600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>928700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>977500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>979900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2242200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1067600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>895300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1087000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2325400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2468900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2369200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2495800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2292400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2306400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2163100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2381500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2249800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2155100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1997800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2117300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1960000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1956600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1888600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2042800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>679300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>770600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>665700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>735700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>768400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>692700</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>722500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>850800</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>834200</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>722000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3303100</v>
+      </c>
+      <c r="E60" s="3">
         <v>3184400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3228600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3889800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3486900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8236800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8585900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6413300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5999900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4756300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4696700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4647900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4150300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4141500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4225200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>4683100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4380500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4289900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4176600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4291200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3722700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3902200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3730300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>4042300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4278800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>4504200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3546500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4179700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>4094000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3979300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2095700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2135700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1907400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1917200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2859100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2039900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2084700</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2240600</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2105900</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>2134200</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6659800</v>
+      </c>
+      <c r="E61" s="3">
         <v>6588100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6055400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6063800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6066500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5936100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5869900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8010200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8011300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>8839600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6468600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8965000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8871700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8691700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3421600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3420400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3419300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3418100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3417000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3231100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3229500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3227800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3226200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3225300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3224300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3223300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3522200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3520200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3518600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3516900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>4265300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>5043800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>5131000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>5134600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>4862100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>5662700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>5706500</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>6249300</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>6293700</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>7068200</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>293500</v>
+      </c>
+      <c r="E62" s="3">
         <v>280000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>274000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>237500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>226400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>213500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>210800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>308700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>309200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>299500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2704000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>254800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>267400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>267900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6623800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6530700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6480000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6422800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6409700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>6623300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>6481300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>6509400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>6454200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>6423500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>6354300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>6223700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>6251100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>5920900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6015500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>6102200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1497300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1526700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1417700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1419600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1429300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1911100</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1880900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>1895800</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>1912500</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>1944900</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10604300</v>
+      </c>
+      <c r="E66" s="3">
         <v>10316800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9711300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10191600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9779800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14386400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14666600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15696700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15237100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14797800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14710400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15033000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14397000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14208900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14270600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14634200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14279800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14130800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14003300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14145600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>13433500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>13639400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>13410700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13691100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13857400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>13951200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>13319800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>13620800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>13628100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>13598400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>7858300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>8706200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>8456100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>8471400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>9150500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>9613700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>9672100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>10385700</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>10312100</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>11147300</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,89 +7909,92 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3478900</v>
+      </c>
+      <c r="E72" s="3">
         <v>3556600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3803600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3517800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3657000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3956300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3941500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7637400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7404100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7355800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7124600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8834400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8622400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8422000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>8123000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7670800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7403900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7044000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6507600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6053400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5836600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5554200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5179700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>4676900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>4346900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4085400</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>8</v>
       </c>
@@ -7831,38 +8004,41 @@
       <c r="AF72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH72" s="3">
         <v>3076100</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AK72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL72" s="3">
         <v>4666900</v>
       </c>
-      <c r="AL72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM72" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AO72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP72" s="3">
         <v>2952600</v>
       </c>
-      <c r="AP72" s="3" t="s">
+      <c r="AQ72" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3425300</v>
+      </c>
+      <c r="E76" s="3">
         <v>3507000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3754900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3464700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3605100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3904800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3977400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7636100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7379500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7312400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7313100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8998200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9031000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8899700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8751500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8275300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8396500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8241500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7718500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7244400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7011700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7411300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7285300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6961100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6813600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6520600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6254800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6121300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5865700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5755900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5642900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>7943100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>7647500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>7355700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>7182300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>6116500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>5860200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>5609000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>5389500</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>5047700</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,257 +8659,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E80" s="2">
         <v>46144</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45962</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45871</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45780</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45689</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45598</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45507</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45416</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45325</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45136</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45045</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44954</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44863</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44772</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44590</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44499</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44317</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44226</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44044</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43953</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43862</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43771</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43680</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43589</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43498</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43407</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43316</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43225</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43134</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43036</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42945</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42854</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42763</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>514500</v>
+      </c>
+      <c r="E81" s="3">
         <v>347300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>506100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>244600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>188400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>343400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3695900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>233300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>132400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>300100</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O81" s="3">
         <v>212000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>200400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>299000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>452200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>266900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>359900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>536400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>454200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>216800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>282400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>374500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>502800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>330000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>261500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>247600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>123000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>255800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>180300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>267900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-2307000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>281800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>273900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>160500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1040100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>239900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>233800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>200500</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>321800</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>171600</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>162000</v>
+      </c>
+      <c r="E83" s="3">
         <v>151100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>149800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>135500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>122600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>119000</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" s="3">
         <v>215800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>202600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>196400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>196500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>189000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>193500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>188900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>196500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>189000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>193500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>188900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>188700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>178500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>176100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>172700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>182900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>170100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>168100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>165500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>179100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>160000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>155100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>151200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>166700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>150400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>152500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>151500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>156600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>149400</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>151300</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>153900</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>155700</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>157600</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>921500</v>
+      </c>
+      <c r="E89" s="3">
         <v>644000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1232200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>319300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>419700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>483000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1025900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>699100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>695700</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O89" s="3">
         <v>505800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>171800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>752000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>880700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>213500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-17900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>538500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>412800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>282600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>179900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>556200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>982600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>296700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>478000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>959000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>855300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>170500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>229900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>614100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>715100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>282100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>381200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>387600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>917600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-82600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>244500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>430700</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1018000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-25000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,130 +9881,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-246300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-252500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-263700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-376400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-245100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-248800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-294800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-341400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-347800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-316500</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="N91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O91" s="3">
         <v>-541300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-425400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-350400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-327900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-392500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-277100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-256300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-273200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-295600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-228900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-898300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>2300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>1000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>206500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-209200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-194400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-622300</v>
-      </c>
-      <c r="AI91" s="3">
-        <v>-200</v>
       </c>
       <c r="AJ91" s="3">
         <v>-200</v>
       </c>
       <c r="AK91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-632100</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>271600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-161400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-110300</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-114100</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-95600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-246900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-252900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-255700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-371800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>223100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-244300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-287900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-322600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-165900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-473000</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O94" s="3">
         <v>-541300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-428300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-352700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-327900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-392500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-277100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-256300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-273600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-294800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-228700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-222800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-182200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-236400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-235200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-235900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-251500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-280000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-296300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-192400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-197300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-224700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-213600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-181100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-182400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-175900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-161500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-108100</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-115300</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-95900</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,8 +10426,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10238,8 +10471,8 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10316,8 +10549,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,370 +10924,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-622900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-853400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-67500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1196600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-439400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-248000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>122900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-287800</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O100" s="3">
         <v>-29700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-104600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-167600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-349000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-54500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-234200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-49100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>145100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-704200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-276600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-503200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-692100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-248200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>493600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-497800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-58000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-36500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-117500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-779300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>3100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>5100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-828800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-37900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-34500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-545500</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-33600</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-770500</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-238100</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K101" s="3">
         <v>-2000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-300</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>400</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-200</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-500</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>400</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E102" s="3">
         <v>290000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>123400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-120000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-553900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-200000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>738500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>128300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-47300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-65500</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>-67200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-359200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>230700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>204400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-235500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-529500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>233600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>283500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-12900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-753100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>57200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>298400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-632000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-4800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1216000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>105700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-168000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-102200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>303800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-261600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>61000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>172100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-622600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>697700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-293200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-461600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>288500</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>132600</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-359400</v>
       </c>
     </row>
